--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2190.4</v>
+        <v>2188</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2925,12 +2925,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AADHARHFC</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aadhar Housing Finance Ltd.</t>
+          <t>Capri Global Capital Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2944,16 +2944,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>461.5</v>
+        <v>224.03</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>449.8 - 453.05 DR DEMAND</t>
+          <t>218.59 - 220.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3027,17 +3027,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capri Global Capital Ltd.</t>
+          <t>Cummins India Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3046,31 +3046,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>224.38</v>
+        <v>5107.5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>218.59 - 220.8 DR DEMAND</t>
+          <t>5037.62 - 5058.05 DR DEMAND</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>4357.85 - 4463.08 DR DEMAND</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3129,17 +3129,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cummins India Ltd.</t>
+          <t>HCL Technologies Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3148,11 +3148,11 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5107.5</v>
+        <v>1302.5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>5037.62 - 5058.05 DR DEMAND</t>
+          <t>1292.5 - 1298.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4357.85 - 4463.08 DR DEMAND</t>
+          <t>1019.59 - 1059.19 DR DEMAND</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3231,12 +3231,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HCL Technologies Ltd.</t>
+          <t>MphasiS Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3250,11 +3250,11 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1302.5</v>
+        <v>2430</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1292.5 - 1298.0 DR DEMAND</t>
+          <t>2395.8 - 2415.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1019.59 - 1059.19 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3333,17 +3333,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>SHYAMMETL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MphasiS Ltd.</t>
+          <t>Shyam Metalics and Energy Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3352,28 +3352,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2430</v>
+        <v>984.9</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2395.8 - 2415.0 DR DEMAND</t>
+          <t>970.0 - 978.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>6.0 B</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>742.73 - 767.72 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
           <t>7.0 A</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3435,17 +3435,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SHYAMMETL</t>
+          <t>WHIRLPOOL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shyam Metalics and Energy Ltd.</t>
+          <t>Whirlpool of India Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3454,31 +3454,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>984.9</v>
+        <v>768.5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>970.0 - 978.7 DR DEMAND</t>
+          <t>751.0 - 753.45 DR DEMAND</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>742.73 - 767.72 DR DEMAND</t>
+          <t>756.85 - 774.65 DR DEMAND</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3518,16 +3518,24 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>1M SCORE &lt;7 | 1D SCORE &lt;7 | SECTOR CONSUMPTION (backtest -ve)</t>
+        </is>
+      </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
@@ -3537,17 +3545,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>WHIRLPOOL</t>
+          <t>YESBANK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Whirlpool of India Ltd.</t>
+          <t>Yes Bank Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3556,31 +3564,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>768.5</v>
+        <v>22.8</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>751.0 - 753.45 DR DEMAND</t>
+          <t>22.42 - 22.46 DR DEMAND</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>756.85 - 774.65 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3595,7 +3603,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3620,24 +3628,16 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>1M SCORE &lt;7 | 1D SCORE &lt;7 | SECTOR CONSUMPTION (backtest -ve)</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
@@ -3647,17 +3647,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>YESBANK</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Yes Bank Ltd.</t>
+          <t>Bajaj Holdings &amp; Investment Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3666,28 +3666,28 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>22.8</v>
+        <v>11320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>22.42 - 22.46 DR DEMAND</t>
+          <t>11219.0 - 11263.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>5.5 B</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>8482.6 - 8638.66 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3749,17 +3749,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bajaj Holdings &amp; Investment Ltd.</t>
+          <t>Bharat Heavy Electricals Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3768,11 +3768,11 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>11320</v>
+        <v>413</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>11219.0 - 11263.0 DR DEMAND</t>
+          <t>402.15 - 405.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8482.6 - 8638.66 DR DEMAND</t>
+          <t>204.46 - 207.34 DR DEMAND</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3851,17 +3851,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>SIGNATURE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bharat Heavy Electricals Ltd.</t>
+          <t>Signatureglobal (India) Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3870,36 +3870,36 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>413</v>
+        <v>795.3</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>402.15 - 405.0 DR DEMAND</t>
+          <t>781.0 - 784.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>204.46 - 207.34 DR DEMAND</t>
+          <t>989.8 - 1111.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3953,17 +3953,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CESC Ltd.</t>
+          <t>Sun Pharmaceutical Industries Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3972,11 +3972,11 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>155.25</v>
+        <v>1902.4</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>153.25 - 153.48 DR DEMAND</t>
+          <t>1868.3 - 1871.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>133.19 - 139.44 DR DEMAND</t>
+          <t>1569.37 - 1580.86 DR DEMAND</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4055,17 +4055,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SIGNATURE</t>
+          <t>BAYERCROP</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Signatureglobal (India) Ltd.</t>
+          <t>Bayer Cropscience Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4074,26 +4074,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>795.3</v>
+        <v>4071.5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>781.0 - 784.9 DR DEMAND</t>
+          <t>4030.0 - 4045.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>989.8 - 1111.0 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -4157,17 +4157,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>CANFINHOME</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Ltd.</t>
+          <t>Can Fin Homes Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4176,31 +4176,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1902.4</v>
+        <v>830.45</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1868.3 - 1871.0 DR DEMAND</t>
+          <t>807.0 - 814.35 DR DEMAND</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1569.37 - 1580.86 DR DEMAND</t>
+          <t>545.13 - 563.82 DR DEMAND</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -4259,17 +4259,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BAYERCROP</t>
+          <t>GRAPHITE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bayer Cropscience Ltd.</t>
+          <t>Graphite India Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4278,36 +4278,36 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4059.5</v>
+        <v>710.75</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>4030.0 - 4045.8 DR DEMAND</t>
+          <t>705.5 - 709.95 DR DEMAND</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>551.99 - 610.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4361,17 +4361,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CANFINHOME</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Can Fin Homes Ltd.</t>
+          <t>Indraprastha Gas Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4380,28 +4380,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>830.45</v>
+        <v>147.87</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>807.0 - 814.35 DR DEMAND</t>
+          <t>151.0 - 153.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>5.5 B</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>141.74 - 145.62 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>545.13 - 563.82 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>6.0 B</t>
-        </is>
-      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -4439,12 +4439,12 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4463,17 +4463,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GRAPHITE</t>
+          <t>MEDANTA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Graphite India Ltd.</t>
+          <t>Global Health Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4482,26 +4482,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>710.75</v>
+        <v>1409.7</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>705.5 - 709.95 DR DEMAND</t>
+          <t>1382.71 - 1393.91 DR DEMAND</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>551.99 - 610.0 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4565,17 +4565,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>NAVA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Indraprastha Gas Ltd.</t>
+          <t>Nava Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4584,26 +4584,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>147.87</v>
+        <v>558.95</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>151.0 - 153.0 RD SUPPLY</t>
+          <t>545.15 - 549.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>141.74 - 145.62 DR DEMAND</t>
+          <t>497.01 - 517.17 DR DEMAND</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4667,17 +4667,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MEDANTA</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Global Health Ltd.</t>
+          <t>Navin Fluorine International Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4686,26 +4686,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1409.7</v>
+        <v>8206.5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1382.71 - 1393.91 DR DEMAND</t>
+          <t>8110.0 - 8151.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>4173.89 - 4245.43 DR DEMAND</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4769,12 +4769,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NAVA</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nava Ltd.</t>
+          <t>NLC India Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4788,11 +4788,11 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>558.95</v>
+        <v>269.8</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>545.15 - 549.2 DR DEMAND</t>
+          <t>263.3 - 267.45 DR DEMAND</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>497.01 - 517.17 DR DEMAND</t>
+          <t>217.6 - 220.69 DR DEMAND</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4871,17 +4871,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Navin Fluorine International Ltd.</t>
+          <t>Tata Power Co. Ltd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4890,36 +4890,36 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>8206.5</v>
+        <v>374.3</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>8110.0 - 8151.0 DR DEMAND</t>
+          <t>367.85 - 371.35 DR DEMAND</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
+          <t>6.0 B</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>322.44 - 334.69 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
           <t>5.0 C</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>4173.89 - 4245.43 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>7.5 A</t>
-        </is>
-      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4973,17 +4973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>TRITURBINE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NLC India Ltd.</t>
+          <t>Triveni Turbine Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4992,11 +4992,11 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>269.8</v>
+        <v>574.85</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>263.3 - 267.45 DR DEMAND</t>
+          <t>561.05 - 569.65 DR DEMAND</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>217.6 - 220.69 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5075,17 +5075,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tata Power Co. Ltd.</t>
+          <t>UPL Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5094,26 +5094,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>374.3</v>
+        <v>569</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>367.85 - 371.35 DR DEMAND</t>
+          <t>557.75 - 559.63 DR DEMAND</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>322.44 - 334.69 DR DEMAND</t>
+          <t>557.75 - 565.72 DR DEMAND</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5158,16 +5158,24 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>TESTED ZONE (2 tests) | 1M SCORE &lt;7 | 1D SCORE &lt;7</t>
+        </is>
+      </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
@@ -5177,17 +5185,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TRITURBINE</t>
+          <t>ABFRL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Triveni Turbine Ltd.</t>
+          <t>Aditya Birla Fashion and Retail Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5196,16 +5204,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>574.85</v>
+        <v>54.35</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>561.05 - 569.65 DR DEMAND</t>
+          <t>53.51 - 53.89 DR DEMAND</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5235,12 +5243,12 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -5279,17 +5287,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>UPL Ltd.</t>
+          <t>Bajaj Finance Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5298,36 +5306,36 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>569</v>
+        <v>1095</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>557.75 - 559.63 DR DEMAND</t>
+          <t>1070.8 - 1078.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>557.75 - 565.72 DR DEMAND</t>
+          <t>783.09 - 796.65 DR DEMAND</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5342,7 +5350,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -5362,24 +5370,16 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>TESTED ZONE (2 tests) | 1M SCORE &lt;7 | 1D SCORE &lt;7</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
@@ -5389,17 +5389,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ABFRL</t>
+          <t>NUVOCO</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Aditya Birla Fashion and Retail Ltd.</t>
+          <t>Nuvoco Vistas Corporation Ltd.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5408,26 +5408,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>54.38</v>
+        <v>322.05</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>53.51 - 53.89 DR DEMAND</t>
+          <t>317.0 - 317.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>349.75 - 398.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5491,12 +5491,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bajaj Finance Ltd.</t>
+          <t>Computer Age Management Services Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5510,31 +5510,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1095</v>
+        <v>753</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1070.8 - 1078.0 DR DEMAND</t>
+          <t>737.82 - 743.27 DR DEMAND</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>783.09 - 796.65 DR DEMAND</t>
+          <t>591.51 - 613.37 DR DEMAND</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5593,17 +5593,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NUVOCO</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nuvoco Vistas Corporation Ltd.</t>
+          <t>Fortis Healthcare Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5612,21 +5612,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>322.05</v>
+        <v>907.1</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>317.0 - 317.8 DR DEMAND</t>
+          <t>879.1 - 892.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>349.75 - 398.0 RD SUPPLY</t>
+          <t>765.99 - 794.16 DR DEMAND</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5695,17 +5695,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Computer Age Management Services Ltd.</t>
+          <t>Indus Towers Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5714,26 +5714,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>753</v>
+        <v>375.75</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>737.82 - 743.27 DR DEMAND</t>
+          <t>367.35 - 368.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>591.51 - 613.37 DR DEMAND</t>
+          <t>427.61 - 433.1 RD SUPPLY</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5797,17 +5797,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fortis Healthcare Ltd.</t>
+          <t>Marico Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5816,36 +5816,36 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>907.1</v>
+        <v>849.25</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>879.1 - 892.9 DR DEMAND</t>
+          <t>832.19 - 836.28 DR DEMAND</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>765.99 - 794.16 DR DEMAND</t>
+          <t>705.08 - 721.7 DR DEMAND</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -5899,12 +5899,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>TRIDENT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Indus Towers Ltd.</t>
+          <t>Trident Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5918,11 +5918,11 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>375.75</v>
+        <v>24.39</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>367.35 - 368.8 DR DEMAND</t>
+          <t>24.14 - 24.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>427.61 - 433.1 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6001,17 +6001,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Marico Ltd.</t>
+          <t>Bajaj Auto Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6020,26 +6020,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>849.25</v>
+        <v>11700</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>832.19 - 836.28 DR DEMAND</t>
+          <t>11541.0 - 11600.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>705.08 - 721.7 DR DEMAND</t>
+          <t>9501.0 - 9716.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -6103,17 +6103,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TRIDENT</t>
+          <t>CHOLAHLDNG</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Trident Ltd.</t>
+          <t>Cholamandalam Financial Holdings Ltd.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6122,28 +6122,28 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>24.39</v>
+        <v>1561.8</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>24.14 - 24.3 DR DEMAND</t>
+          <t>1540.48 - 1544.68 DR DEMAND</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
+          <t>4.5 C</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>1358.29 - 1396.78 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J56" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -6205,17 +6205,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>JSWCEMENT</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bajaj Auto Ltd.</t>
+          <t>JSW Cement Ltd.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6224,36 +6224,36 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>11700</v>
+        <v>126.04</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>11541.0 - 11600.0 DR DEMAND</t>
+          <t>122.35 - 124.18 DR DEMAND</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>9501.0 - 9716.0 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6307,17 +6307,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CHOLAHLDNG</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cholamandalam Financial Holdings Ltd.</t>
+          <t>Mahindra &amp; Mahindra Ltd.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6326,36 +6326,36 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1561.8</v>
+        <v>3412.2</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1540.48 - 1544.68 DR DEMAND</t>
+          <t>3384.6 - 3401.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1358.29 - 1396.78 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6409,17 +6409,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>JSWCEMENT</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JSW Cement Ltd.</t>
+          <t>SBI Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6428,28 +6428,28 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>126.04</v>
+        <v>1792.9</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>122.35 - 124.18 DR DEMAND</t>
+          <t>1700.4 - 1706.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
+          <t>6.0 B</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>1700.4 - 1765.7 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
           <t>4.5 C</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J59" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -6487,12 +6487,12 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6511,17 +6511,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Ltd.</t>
+          <t>Zydus Lifesciences Ltd.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -6530,26 +6530,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3412.2</v>
+        <v>1120</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>3384.6 - 3401.0 DR DEMAND</t>
+          <t>1094.12 - 1098.81 DR DEMAND</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>855.18 - 875.51 DR DEMAND</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6613,17 +6613,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SBI Life Insurance Company Ltd.</t>
+          <t>Adani Green Energy Ltd.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6632,21 +6632,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1792.9</v>
+        <v>1320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1700.4 - 1706.0 DR DEMAND</t>
+          <t>1291.4 - 1302.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1700.4 - 1765.7 DR DEMAND</t>
+          <t>765.0 - 814.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6715,17 +6715,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Ltd.</t>
+          <t>Asian Paints Ltd.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6734,28 +6734,28 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1120</v>
+        <v>2640</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1094.12 - 1098.81 DR DEMAND</t>
+          <t>2624.0 - 2635.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
+          <t>4.0 C</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2083.96 - 2137.91 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
           <t>4.5 C</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>855.18 - 875.51 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>4.0 C</t>
-        </is>
-      </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6817,17 +6817,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Adani Green Energy Ltd.</t>
+          <t>Indian Energy Exchange Ltd.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -6836,11 +6836,11 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1320</v>
+        <v>123.7</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1291.4 - 1302.1 DR DEMAND</t>
+          <t>120.91 - 122.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>765.0 - 814.2 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6919,17 +6919,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>RHIM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Asian Paints Ltd.</t>
+          <t>RHI MAGNESITA INDIA LTD.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6938,11 +6938,11 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2640</v>
+        <v>375.25</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2624.0 - 2635.7 DR DEMAND</t>
+          <t>366.95 - 370.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6952,17 +6952,17 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2083.96 - 2137.91 DR DEMAND</t>
+          <t>323.05 - 337.85 DR DEMAND</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7021,17 +7021,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>TECHNOE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Indian Energy Exchange Ltd.</t>
+          <t>Techno Electric &amp; Engineering Company Ltd.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -7040,28 +7040,28 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>123.7</v>
+        <v>987.45</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>120.91 - 122.0 DR DEMAND</t>
+          <t>1085.3 - 1092.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>870.0 - 974.5 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
           <t>4.0 C</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J65" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -7099,12 +7099,12 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7123,17 +7123,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>RHIM</t>
+          <t>ECLERX</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RHI MAGNESITA INDIA LTD.</t>
+          <t>eClerx Services Ltd.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -7142,36 +7142,36 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>375.25</v>
+        <v>1815.7</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>366.95 - 370.0 DR DEMAND</t>
+          <t>1734.04 - 1810.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>323.05 - 337.85 DR DEMAND</t>
+          <t>1083.13 - 1256.54 DR DEMAND</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -7225,17 +7225,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TECHNOE</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Techno Electric &amp; Engineering Company Ltd.</t>
+          <t>Havells India Ltd.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -7244,36 +7244,36 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>987.45</v>
+        <v>1268</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1085.3 - 1092.0 RD SUPPLY</t>
+          <t>1256.9 - 1260.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>870.0 - 974.5 DR DEMAND</t>
+          <t>1390.17 - 1435.15 RD SUPPLY</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7283,12 +7283,12 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7327,17 +7327,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ECLERX</t>
+          <t>WAAREEENER</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>eClerx Services Ltd.</t>
+          <t>Waaree Energies Ltd.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7346,11 +7346,11 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1815.7</v>
+        <v>2678.2</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1734.04 - 1810.7 DR DEMAND</t>
+          <t>2656.9 - 2660.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -7360,22 +7360,22 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1083.13 - 1256.54 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7429,12 +7429,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Havells India Ltd.</t>
+          <t>PG Electroplast Ltd.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7448,26 +7448,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1268</v>
+        <v>600.55</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1256.9 - 1260.7 DR DEMAND</t>
+          <t>594.25 - 600.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1390.17 - 1435.15 RD SUPPLY</t>
+          <t>811.74 - 836.08 RD SUPPLY</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -7531,17 +7531,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>WAAREEENER</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Waaree Energies Ltd.</t>
+          <t>Tata Steel Ltd.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -7550,26 +7550,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2678.2</v>
+        <v>183</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2656.9 - 2660.9 DR DEMAND</t>
+          <t>182.01 - 182.63 DR DEMAND</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>156.83 - 164.57 DR DEMAND</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -7633,17 +7633,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>ERIS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PG Electroplast Ltd.</t>
+          <t>Eris Lifesciences Ltd.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -7652,36 +7652,36 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>600.55</v>
+        <v>1328.2</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>594.25 - 600.1 DR DEMAND</t>
+          <t>1315.44 - 1323.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>811.74 - 836.08 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>4.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7735,17 +7735,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>INTELLECT</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tata Steel Ltd.</t>
+          <t>Intellect Design Arena Ltd.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -7754,26 +7754,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>183</v>
+        <v>691.25</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>182.01 - 182.63 DR DEMAND</t>
+          <t>675.15 - 678.96 DR DEMAND</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>156.83 - 164.57 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7793,12 +7793,12 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>4.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7837,17 +7837,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ERIS</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Eris Lifesciences Ltd.</t>
+          <t>Pidilite Industries Ltd.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -7856,16 +7856,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1328.2</v>
+        <v>1649</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1315.44 - 1323.5 DR DEMAND</t>
+          <t>1648.1 - 1660.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7895,22 +7895,22 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>4.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -7939,17 +7939,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>INTELLECT</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Intellect Design Arena Ltd.</t>
+          <t>Chambal Fertilizers &amp; Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -7958,28 +7958,28 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>691.25</v>
+        <v>431.15</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>675.15 - 678.96 DR DEMAND</t>
+          <t>430.45 - 433.07 DR DEMAND</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
+          <t>4.5 C</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>404.75 - 434.2 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
           <t>3.0 C</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7997,22 +7997,22 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>4.0 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>APPROACHING DEMAND</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -8022,16 +8022,24 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>TESTED ZONE (1 tests) | 1M SCORE &lt;7 | 1D SCORE &lt;7</t>
+        </is>
+      </c>
       <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr"/>
@@ -8041,17 +8049,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>HEXT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Pidilite Industries Ltd.</t>
+          <t>Hexaware Technologies Ltd.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -8060,16 +8068,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1649</v>
+        <v>532.45</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1648.1 - 1660.0 DR DEMAND</t>
+          <t>532.0 - 536.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8084,12 +8092,12 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -8099,12 +8107,12 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -8143,55 +8151,55 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Chambal Fertilizers &amp; Chemicals Ltd.</t>
+          <t>RITES Ltd.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>EQUILIBRIUM</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>431.75</v>
+        <v>218.08</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>430.45 - 433.07 DR DEMAND</t>
+          <t>212.73 - 214.85 DR DEMAND</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>404.75 - 434.2 DR DEMAND</t>
+          <t>217.6 - 229.47 RD SUPPLY</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -8201,7 +8209,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -8216,7 +8224,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CONFLICT</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -8241,7 +8249,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>TESTED ZONE (1 tests) | 1M SCORE &lt;7 | 1D SCORE &lt;7</t>
+          <t>SUPPLY/EQ - long system me nahi | 1M SCORE &lt;7</t>
         </is>
       </c>
       <c r="V76" t="inlineStr"/>
@@ -8253,17 +8261,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HEXT</t>
+          <t>ABDL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Hexaware Technologies Ltd.</t>
+          <t>Allied Blenders and Distillers Ltd.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8272,36 +8280,36 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>532.45</v>
+        <v>595</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>532.0 - 536.6 DR DEMAND</t>
+          <t>584.75 - 598.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>378.82 - 400.58 DR DEMAND</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -8311,12 +8319,12 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -8355,55 +8363,55 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RITES Ltd.</t>
+          <t>CESC Ltd.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>218.08</v>
+        <v>155.09</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>212.73 - 214.85 DR DEMAND</t>
+          <t>154.67 - 155.21 DR DEMAND</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>217.6 - 229.47 RD SUPPLY</t>
+          <t>133.19 - 139.44 DR DEMAND</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8413,12 +8421,12 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -8428,7 +8436,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>CONFLICT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -8438,24 +8446,16 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>SUPPLY/EQ - long system me nahi | 1M SCORE &lt;7</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
@@ -8465,12 +8465,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>LINDEINDIA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Allied Blenders and Distillers Ltd.</t>
+          <t>Linde India Ltd.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8484,11 +8484,11 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>597.85</v>
+        <v>6672</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>584.75 - 598.5 DR DEMAND</t>
+          <t>6546.9 - 6753.55 DR DEMAND</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -8498,22 +8498,22 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>378.82 - 400.58 DR DEMAND</t>
+          <t>7487.35 - 7842.09 RD SUPPLY</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -8567,17 +8567,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LINDEINDIA</t>
+          <t>GALLANTT</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Linde India Ltd.</t>
+          <t>Gallantt Ispat Ltd.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -8586,26 +8586,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6672</v>
+        <v>584.4</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>6546.9 - 6753.55 DR DEMAND</t>
+          <t>572.25 - 585.35 DR DEMAND</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>7487.35 - 7842.09 RD SUPPLY</t>
+          <t>861.85 - 948.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -8669,12 +8669,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GALLANTT</t>
+          <t>INDIACEM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Gallantt Ispat Ltd.</t>
+          <t>India Cements Ltd.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8688,11 +8688,11 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>584.4</v>
+        <v>370.9</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>572.25 - 585.35 DR DEMAND</t>
+          <t>366.25 - 371.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -8702,12 +8702,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>861.85 - 948.0 RD SUPPLY</t>
+          <t>400.0 - 416.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8771,55 +8771,55 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>INDIACEM</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>India Cements Ltd.</t>
+          <t>Eicher Motors Ltd.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>SUPPLY</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>370.9</v>
+        <v>8010</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>366.25 - 371.8 DR DEMAND</t>
+          <t>8134.81 - 8144.71 RD SUPPLY</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>400.0 - 416.4 RD SUPPLY</t>
+          <t>7927.48 - 8144.71 RD SUPPLY</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8829,22 +8829,22 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -8854,16 +8854,24 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SUPPLY/EQ - long system me nahi | TESTED ZONE (1 tests) | 1D SCORE &lt;7</t>
+        </is>
+      </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
@@ -8873,17 +8881,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Eicher Motors Ltd.</t>
+          <t>Alkem Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -8892,36 +8900,36 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>8010</v>
+        <v>5400</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>8134.81 - 8144.71 RD SUPPLY</t>
+          <t>5475.0 - 5510.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>7927.48 - 8144.71 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8936,7 +8944,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>8.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8956,24 +8964,16 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>SUPPLY/EQ - long system me nahi | TESTED ZONE (1 tests) | 1D SCORE &lt;7</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
       <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
@@ -8983,17 +8983,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Alkem Laboratories Ltd.</t>
+          <t>Bank of Baroda</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -9002,11 +9002,11 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5395</v>
+        <v>247</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>5475.0 - 5510.0 RD SUPPLY</t>
+          <t>251.0 - 251.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>178.57 - 184.54 DR DEMAND</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9085,17 +9085,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>SUNDARMFIN</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Bank of Baroda</t>
+          <t>Sundaram Finance Ltd.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -9104,11 +9104,11 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>247</v>
+        <v>4534.5</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>251.0 - 251.4 RD SUPPLY</t>
+          <t>4625.4 - 4658.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>178.57 - 184.54 DR DEMAND</t>
+          <t>5480.6 - 5612.41 RD SUPPLY</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -9187,17 +9187,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SUNDARMFIN</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sundaram Finance Ltd.</t>
+          <t>Colgate Palmolive (India) Ltd.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -9206,26 +9206,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4534.5</v>
+        <v>1889</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>4625.4 - 4658.0 RD SUPPLY</t>
+          <t>1910.0 - 1914.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>5480.6 - 5612.41 RD SUPPLY</t>
+          <t>2228.23 - 2274.78 RD SUPPLY</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -9289,12 +9289,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>EMAMILTD</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Colgate Palmolive (India) Ltd.</t>
+          <t>Emami Ltd.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9308,11 +9308,11 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1889</v>
+        <v>402.6</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1910.0 - 1914.9 RD SUPPLY</t>
+          <t>407.4 - 413.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -9322,12 +9322,12 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2228.23 - 2274.78 RD SUPPLY</t>
+          <t>444.5 - 477.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -9391,17 +9391,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EMAMILTD</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Emami Ltd.</t>
+          <t>Adani Enterprises Ltd.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -9410,31 +9410,31 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>402.6</v>
+        <v>2997</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>407.4 - 413.0 RD SUPPLY</t>
+          <t>3049.0 - 3058.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>444.5 - 477.0 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -9493,17 +9493,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>HDBFS</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Adani Enterprises Ltd.</t>
+          <t>HDB Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -9512,11 +9512,11 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2997</v>
+        <v>695.85</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>3049.0 - 3058.6 RD SUPPLY</t>
+          <t>700.0 - 701.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -9595,12 +9595,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HDBFS</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HDB Financial Services Ltd.</t>
+          <t>HDFC Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -9614,31 +9614,31 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>695.85</v>
+        <v>554.8</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>700.0 - 701.0 RD SUPPLY</t>
+          <t>561.0 - 561.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>811.41 - 817.84 RD SUPPLY</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -9697,17 +9697,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>J&amp;KBANK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Company Ltd.</t>
+          <t>Jammu &amp; Kashmir Bank Ltd.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -9716,11 +9716,11 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>554.8</v>
+        <v>149.01</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>561.0 - 561.95 RD SUPPLY</t>
+          <t>151.37 - 152.17 RD SUPPLY</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -9730,12 +9730,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>811.41 - 817.84 RD SUPPLY</t>
+          <t>108.0 - 110.01 DR DEMAND</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9799,17 +9799,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>J&amp;KBANK</t>
+          <t>LATENTVIEW</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir Bank Ltd.</t>
+          <t>Latent View Analytics Ltd.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -9818,11 +9818,11 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>149.01</v>
+        <v>278.1</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>151.37 - 152.17 RD SUPPLY</t>
+          <t>281.75 - 285.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -9832,12 +9832,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>108.0 - 110.01 DR DEMAND</t>
+          <t>262.05 - 270.8 DR DEMAND</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -9901,17 +9901,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Latent View Analytics Ltd.</t>
+          <t>Supreme Industries Ltd.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -9920,31 +9920,31 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>278.1</v>
+        <v>3642</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>281.75 - 285.5 RD SUPPLY</t>
+          <t>3713.74 - 3719.99 RD SUPPLY</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>262.05 - 270.8 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -10003,17 +10003,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Supreme Industries Ltd.</t>
+          <t>Dixon Technologies (India) Ltd.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -10022,26 +10022,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3642</v>
+        <v>14850</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>3713.74 - 3719.99 RD SUPPLY</t>
+          <t>14860.0 - 14890.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>16444.68 - 17061.41 RD SUPPLY</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -10105,12 +10105,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>BHARTIHEXA</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Dixon Technologies (India) Ltd.</t>
+          <t>Bharti Hexacom Ltd.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10124,26 +10124,26 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>14850</v>
+        <v>1591.2</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>14860.0 - 14890.0 RD SUPPLY</t>
+          <t>1615.6 - 1631.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>16444.68 - 17061.41 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -10207,17 +10207,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>BLUEJET</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Clean Science and Technology Ltd.</t>
+          <t>Blue Jet Healthcare Ltd.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -10226,11 +10226,11 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>825.5</v>
+        <v>596.15</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>842.0 - 843.85 RD SUPPLY</t>
+          <t>607.95 - 612.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1545.87 - 1590.61 RD SUPPLY</t>
+          <t>883.3 - 966.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -10309,17 +10309,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FIVESTAR</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Five-Star Business Finance Ltd.</t>
+          <t>Clean Science and Technology Ltd.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -10328,11 +10328,11 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>520.95</v>
+        <v>825.5</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>527.95 - 533.0 RD SUPPLY</t>
+          <t>842.0 - 843.85 RD SUPPLY</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>412.05 - 443.54 DR DEMAND</t>
+          <t>1545.87 - 1590.61 RD SUPPLY</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -10411,17 +10411,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>NEULANDLAB</t>
+          <t>FIVESTAR</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Neuland Laboratories Ltd.</t>
+          <t>Five-Star Business Finance Ltd.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -10430,11 +10430,11 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>23301</v>
+        <v>520.95</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>23669.0 - 23735.0 RD SUPPLY</t>
+          <t>527.95 - 533.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -10444,12 +10444,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>10163.49 - 10582.66 DR DEMAND</t>
+          <t>412.05 - 443.54 DR DEMAND</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -10513,17 +10513,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>NEULANDLAB</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Oil India Ltd.</t>
+          <t>Neuland Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -10532,11 +10532,11 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>475</v>
+        <v>23301</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>480.9 - 482.0 RD SUPPLY</t>
+          <t>23669.0 - 23735.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>404.1 - 416.95 DR DEMAND</t>
+          <t>10163.49 - 10582.66 DR DEMAND</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -10615,17 +10615,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>One 97 Communications Ltd.</t>
+          <t>Oil India Ltd.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -10634,11 +10634,11 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1632</v>
+        <v>475</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1649.5 - 1657.6 RD SUPPLY</t>
+          <t>480.9 - 482.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -10648,7 +10648,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>651.5 - 700.0 DR DEMAND</t>
+          <t>404.1 - 416.95 DR DEMAND</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -10717,17 +10717,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AEGISVOPAK</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Aegis Vopak Terminals Ltd.</t>
+          <t>One 97 Communications Ltd.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -10736,26 +10736,26 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>276.3</v>
+        <v>1632</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>277.8 - 280.0 RD SUPPLY</t>
+          <t>1649.5 - 1657.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>651.5 - 700.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -10780,7 +10780,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -10819,17 +10819,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BHARTIHEXA</t>
+          <t>AEGISVOPAK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Bharti Hexacom Ltd.</t>
+          <t>Aegis Vopak Terminals Ltd.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -10838,11 +10838,11 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1592</v>
+        <v>276.3</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1615.6 - 1631.4 RD SUPPLY</t>
+          <t>277.8 - 280.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -10921,12 +10921,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>GROWW</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>HDFC Asset Management Company Ltd.</t>
+          <t>Billionbrains Garage Ventures Ltd.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -10940,26 +10940,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2610</v>
+        <v>197.01</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2729.2 - 2767.3 RD SUPPLY</t>
+          <t>201.0 - 202.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2640.84 - 2839.4 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -10999,12 +10999,12 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -11023,17 +11023,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>LT Foods Ltd.</t>
+          <t>HDFC Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -11042,26 +11042,26 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>427.6</v>
+        <v>2610</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>430.02 - 431.11 RD SUPPLY</t>
+          <t>2729.2 - 2767.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>429.62 - 438.85 RD SUPPLY</t>
+          <t>2640.84 - 2839.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -11111,19 +11111,11 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T104" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>SUPPLY/EQ - long system me nahi | TESTED ZONE (1 tests) | 1M SCORE &lt;7 | 1D SCORE &lt;7</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
       <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr"/>
@@ -11133,12 +11125,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PARADEEP</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Paradeep Phosphates Ltd.</t>
+          <t>LT Foods Ltd.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -11152,26 +11144,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>148.48</v>
+        <v>427.6</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>151.0 - 152.7 RD SUPPLY</t>
+          <t>430.02 - 431.11 RD SUPPLY</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>82.87 - 86.49 DR DEMAND</t>
+          <t>429.62 - 438.85 RD SUPPLY</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -11181,7 +11173,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -11216,16 +11208,24 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T105" t="inlineStr"/>
-      <c r="U105" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SUPPLY/EQ - long system me nahi | TESTED ZONE (1 tests) | 1M SCORE &lt;7 | 1D SCORE &lt;7</t>
+        </is>
+      </c>
       <c r="V105" t="inlineStr"/>
       <c r="W105" t="inlineStr"/>
       <c r="X105" t="inlineStr"/>
@@ -11235,17 +11235,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TEGA</t>
+          <t>PARADEEP</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Tega Industries Ltd.</t>
+          <t>Paradeep Phosphates Ltd.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -11254,11 +11254,11 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1743.2</v>
+        <v>148.48</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1776.5 - 1837.0 RD SUPPLY</t>
+          <t>151.0 - 152.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>1236.4 - 1321.57 DR DEMAND</t>
+          <t>82.87 - 86.49 DR DEMAND</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -11337,17 +11337,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ANURAS</t>
+          <t>TEGA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Anupam Rasayan India Ltd.</t>
+          <t>Tega Industries Ltd.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -11356,36 +11356,36 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1243.7</v>
+        <v>1743.2</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1249.6 - 1259.9 RD SUPPLY</t>
+          <t>1776.5 - 1837.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>600.61 - 631.99 DR DEMAND</t>
+          <t>1236.4 - 1321.57 DR DEMAND</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -11439,17 +11439,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>ANURAS</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Phoenix Mills Ltd.</t>
+          <t>Anupam Rasayan India Ltd.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -11458,36 +11458,36 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1930</v>
+        <v>1243.7</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1939.5 - 1950.0 RD SUPPLY</t>
+          <t>1249.6 - 1259.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1853.5 - 1993.0 RD SUPPLY</t>
+          <t>600.61 - 631.99 DR DEMAND</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -11522,24 +11522,16 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T108" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>SUPPLY/EQ - long system me nahi | TESTED ZONE (2 tests) | 1M SCORE &lt;7 | 1D SCORE &lt;7 | SECTOR REALTY (backtest -ve)</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr"/>
       <c r="W108" t="inlineStr"/>
       <c r="X108" t="inlineStr"/>
@@ -11549,17 +11541,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Hindustan Zinc Ltd.</t>
+          <t>Phoenix Mills Ltd.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -11568,26 +11560,26 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>594.9</v>
+        <v>1930</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>604.25 - 606.2 RD SUPPLY</t>
+          <t>1939.5 - 1950.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>475.32 - 493.14 DR DEMAND</t>
+          <t>1853.5 - 1993.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -11597,12 +11589,12 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -11612,7 +11604,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -11632,16 +11624,24 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T109" t="inlineStr"/>
-      <c r="U109" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>SUPPLY/EQ - long system me nahi | TESTED ZONE (2 tests) | 1M SCORE &lt;7 | 1D SCORE &lt;7 | SECTOR REALTY (backtest -ve)</t>
+        </is>
+      </c>
       <c r="V109" t="inlineStr"/>
       <c r="W109" t="inlineStr"/>
       <c r="X109" t="inlineStr"/>
@@ -11651,17 +11651,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Syngene International Ltd.</t>
+          <t>Hindustan Zinc Ltd.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -11670,41 +11670,41 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>407.25</v>
+        <v>594.9</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>412.0 - 413.9 RD SUPPLY</t>
+          <t>604.25 - 606.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>711.99 - 726.54 RD SUPPLY</t>
+          <t>475.32 - 493.14 DR DEMAND</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -11753,17 +11753,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>TATAINVEST</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Tata Investment Corporation Ltd.</t>
+          <t>Syngene International Ltd.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -11772,26 +11772,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>647.95</v>
+        <v>407.25</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>691.04 - 711.33 RD SUPPLY</t>
+          <t>412.0 - 413.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>655.32 - 737.89 RD SUPPLY</t>
+          <t>711.99 - 726.54 RD SUPPLY</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -11831,12 +11831,12 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -11855,17 +11855,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ZFCVINDIA</t>
+          <t>TATAINVEST</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ZF Commercial Vehicle Control Systems India Ltd.</t>
+          <t>Tata Investment Corporation Ltd.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -11874,31 +11874,31 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2662</v>
+        <v>647.95</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2682.02 - 2695.16 RD SUPPLY</t>
+          <t>691.04 - 711.33 RD SUPPLY</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2260.0 - 2417.9 DR DEMAND</t>
+          <t>655.32 - 737.89 RD SUPPLY</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -11957,17 +11957,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>ZFCVINDIA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Bharat Dynamics Ltd.</t>
+          <t>ZF Commercial Vehicle Control Systems India Ltd.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -11976,28 +11976,28 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1359</v>
+        <v>2662</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>1308.2 - 1317.0 DR DEMAND</t>
+          <t>2682.02 - 2695.16 RD SUPPLY</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
+          <t>5.0 C</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2260.0 - 2417.9 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
           <t>7.5 A</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>1364.1 - 1481.2 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>4.5 C</t>
-        </is>
-      </c>
       <c r="J113" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -12020,7 +12020,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -12035,12 +12035,12 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -12059,12 +12059,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CARBORUNIV</t>
+          <t>BDL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Carborundum Universal Ltd.</t>
+          <t>Bharat Dynamics Ltd.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -12078,11 +12078,11 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1167</v>
+        <v>1359</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1081.4 - 1087.2 DR DEMAND</t>
+          <t>1308.2 - 1317.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1181.58 - 1303.79 RD SUPPLY</t>
+          <t>1364.1 - 1481.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -12112,7 +12112,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -12161,17 +12161,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CENTRALBK</t>
+          <t>CARBORUNIV</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Central Bank of India</t>
+          <t>Carborundum Universal Ltd.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -12180,41 +12180,41 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>31.32</v>
+        <v>1169.8</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>31.46 - 31.6 RD SUPPLY</t>
+          <t>1081.4 - 1087.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>35.83 - 36.93 RD SUPPLY</t>
+          <t>1181.58 - 1303.79 RD SUPPLY</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -12239,12 +12239,12 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -12263,17 +12263,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>CENTRALBK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ICICI Prudential Life Insurance Company Ltd.</t>
+          <t>Central Bank of India</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -12282,11 +12282,11 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>515</v>
+        <v>31.29</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>520.25 - 527.5 RD SUPPLY</t>
+          <t>31.46 - 31.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>35.83 - 36.93 RD SUPPLY</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -12365,17 +12365,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Vodafone Idea Ltd.</t>
+          <t>ICICI Prudential Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -12384,36 +12384,36 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>13.94</v>
+        <v>515</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>14.11 - 14.19 RD SUPPLY</t>
+          <t>520.25 - 527.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>12.6 - 13.01 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -12467,12 +12467,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>JSWDULUX</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>JSW Dulux Ltd.</t>
+          <t>Vodafone Idea Ltd.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -12486,11 +12486,11 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3118.8</v>
+        <v>13.94</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>3169.9 - 3195.0 RD SUPPLY</t>
+          <t>14.11 - 14.19 RD SUPPLY</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -12500,12 +12500,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2862.0 - 2938.8 DR DEMAND</t>
+          <t>12.6 - 13.01 DR DEMAND</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -12569,17 +12569,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>LTTS</t>
+          <t>JSWDULUX</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>JSW Dulux Ltd.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -12588,11 +12588,11 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3604.6</v>
+        <v>3118.8</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>3652.7 - 3708.0 RD SUPPLY</t>
+          <t>3169.9 - 3195.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2976.44 - 3086.89 DR DEMAND</t>
+          <t>2862.0 - 2938.8 DR DEMAND</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -12671,17 +12671,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>LTTS</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Ltd.</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -12690,11 +12690,11 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>990</v>
+        <v>3604.6</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>1001.86 - 1008.21 RD SUPPLY</t>
+          <t>3652.7 - 3708.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -12704,12 +12704,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>835.1 - 851.95 DR DEMAND</t>
+          <t>2976.44 - 3086.89 DR DEMAND</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -12773,17 +12773,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Oberoi Realty Ltd.</t>
+          <t>Motilal Oswal Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -12792,26 +12792,26 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1886</v>
+        <v>990</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>1950.4 - 1960.7 RD SUPPLY</t>
+          <t>1001.86 - 1008.21 RD SUPPLY</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>1903.46 - 1993.03 RD SUPPLY</t>
+          <t>835.1 - 851.95 DR DEMAND</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -12851,12 +12851,12 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -12875,17 +12875,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Oracle Financial Services Software Ltd.</t>
+          <t>Oberoi Realty Ltd.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -12894,21 +12894,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>11724</v>
+        <v>1886</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>11318.0 - 11420.0 DR DEMAND</t>
+          <t>1950.4 - 1960.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>11863.13 - 12262.5 RD SUPPLY</t>
+          <t>1903.46 - 1993.03 RD SUPPLY</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -12977,17 +12977,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PFIZER</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Pfizer Ltd.</t>
+          <t>Oracle Financial Services Software Ltd.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -12996,28 +12996,28 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4978.2</v>
+        <v>11724</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>5067.58 - 5107.14 RD SUPPLY</t>
+          <t>11318.0 - 11420.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>11863.13 - 12262.5 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
           <t>4.5 C</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J123" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -13055,12 +13055,12 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
@@ -13079,17 +13079,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>PFIZER</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>Pfizer Ltd.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -13098,26 +13098,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1048.7</v>
+        <v>4978.2</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>1007.4 - 1015.3 DR DEMAND</t>
+          <t>5067.58 - 5107.14 RD SUPPLY</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>1049.53 - 1101.1 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -13157,12 +13157,12 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -13181,17 +13181,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Shriram Finance Ltd.</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -13200,28 +13200,28 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1130</v>
+        <v>1048.7</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>1141.0 - 1153.7 RD SUPPLY</t>
+          <t>1007.4 - 1015.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
+          <t>2.5 C</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>1049.53 - 1101.1 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
           <t>4.5 C</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>559.9 - 573.24 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>6.5 B</t>
-        </is>
-      </c>
       <c r="J125" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -13259,12 +13259,12 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
@@ -13283,17 +13283,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Sona BLW Precision Forgings Ltd.</t>
+          <t>Shriram Finance Ltd.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -13302,11 +13302,11 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>817.6</v>
+        <v>1130</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>821.9 - 824.6 RD SUPPLY</t>
+          <t>1141.0 - 1153.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>399.83 - 409.23 DR DEMAND</t>
+          <t>559.9 - 573.24 DR DEMAND</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -13385,17 +13385,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>TITAGARH</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Titagarh Rail Systems Ltd.</t>
+          <t>Sona BLW Precision Forgings Ltd.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -13404,11 +13404,11 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>843.55</v>
+        <v>817.6</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>850.75 - 869.9 RD SUPPLY</t>
+          <t>821.9 - 824.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -13418,12 +13418,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>399.84 - 409.23 DR DEMAND</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -13487,17 +13487,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>TITAGARH</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Castrol India Ltd.</t>
+          <t>Titagarh Rail Systems Ltd.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -13506,26 +13506,26 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>187.9</v>
+        <v>843.55</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>189.0 - 190.45 RD SUPPLY</t>
+          <t>850.75 - 869.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>144.37 - 156.26 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -13589,17 +13589,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Granules India Ltd.</t>
+          <t>Castrol India Ltd.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -13608,11 +13608,11 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>858.15</v>
+        <v>187.77</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>874.9 - 883.0 RD SUPPLY</t>
+          <t>189.0 - 190.45 RD SUPPLY</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -13622,12 +13622,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>419.84 - 453.47 DR DEMAND</t>
+          <t>144.37 - 156.26 DR DEMAND</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -13691,17 +13691,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Jubilant Foodworks Ltd.</t>
+          <t>Granules India Ltd.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -13710,11 +13710,11 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>506.75</v>
+        <v>858.15</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>511.5 - 512.6 RD SUPPLY</t>
+          <t>874.9 - 883.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -13724,12 +13724,12 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>699.84 - 715.66 RD SUPPLY</t>
+          <t>419.84 - 453.47 DR DEMAND</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -13793,17 +13793,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Bank of Maharashtra</t>
+          <t>Jubilant Foodworks Ltd.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -13812,11 +13812,11 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>80.42</v>
+        <v>506.75</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>81.75 - 82.19 RD SUPPLY</t>
+          <t>511.5 - 512.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -13826,12 +13826,12 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>91.75 - 94.5 RD SUPPLY</t>
+          <t>699.84 - 715.66 RD SUPPLY</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -13895,17 +13895,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Coforge Ltd.</t>
+          <t>Bank of Maharashtra</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -13914,26 +13914,26 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1891.7</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>1762.2 - 1773.0 DR DEMAND</t>
+          <t>81.75 - 82.19 RD SUPPLY</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>1906.98 - 1973.26 RD SUPPLY</t>
+          <t>91.75 - 94.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -13943,7 +13943,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -13958,7 +13958,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>3.5 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -13973,12 +13973,12 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -13997,17 +13997,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Info Edge (India) Ltd.</t>
+          <t>Coforge Ltd.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -14016,28 +14016,28 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1350.1</v>
+        <v>1891.7</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>1358.81 - 1381.39 RD SUPPLY</t>
+          <t>1762.2 - 1773.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>1906.98 - 1973.26 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
           <t>3.5 C</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>1474.21 - 1535.33 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>6.0 B</t>
-        </is>
-      </c>
       <c r="J133" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -14045,7 +14045,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -14075,12 +14075,12 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
@@ -14099,17 +14099,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>NMDC Ltd.</t>
+          <t>Info Edge (India) Ltd.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -14118,36 +14118,36 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>84.61</v>
+        <v>1350.1</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>85.85 - 86.45 RD SUPPLY</t>
+          <t>1358.81 - 1381.39 RD SUPPLY</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1474.21 - 1535.33 RD SUPPLY</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -14201,17 +14201,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Reliance Industries Ltd.</t>
+          <t>NMDC Ltd.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -14220,11 +14220,11 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1316</v>
+        <v>84.61</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>1328.9 - 1344.9 RD SUPPLY</t>
+          <t>85.85 - 86.45 RD SUPPLY</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -14234,12 +14234,12 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>1424.22 - 1466.62 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -14303,17 +14303,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Hyundai Motor India Ltd.</t>
+          <t>Reliance Industries Ltd.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -14322,36 +14322,36 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2218.8</v>
+        <v>1316</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2223.0 - 2251.5 RD SUPPLY</t>
+          <t>1328.9 - 1344.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1424.22 - 1466.62 RD SUPPLY</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>3.0 / 10 SUPPLY</t>
+          <t>3.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -14405,17 +14405,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Petronet LNG Ltd.</t>
+          <t>Hyundai Motor India Ltd.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -14424,11 +14424,11 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>293</v>
+        <v>2218.8</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>293.32 - 298.51 RD SUPPLY</t>
+          <t>2223.0 - 2251.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -14438,12 +14438,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>232.67 - 245.62 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -14507,17 +14507,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>TBOTEK</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TBO Tek Ltd.</t>
+          <t>Petronet LNG Ltd.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -14526,21 +14526,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1696.5</v>
+        <v>293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>1710.0 - 1734.4 RD SUPPLY</t>
+          <t>293.32 - 298.51 RD SUPPLY</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>1004.2 - 1057.3 DR DEMAND</t>
+          <t>232.67 - 245.62 DR DEMAND</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -14570,7 +14570,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2.5 / 10 SUPPLY</t>
+          <t>3.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -14609,17 +14609,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ELECON</t>
+          <t>TBOTEK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Elecon Engineering Co. Ltd.</t>
+          <t>TBO Tek Ltd.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -14628,36 +14628,36 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>451.55</v>
+        <v>1696.5</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>450.65 - 452.0 RD SUPPLY</t>
+          <t>1710.0 - 1734.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>630.8 - 668.52 RD SUPPLY</t>
+          <t>1004.2 - 1057.3 DR DEMAND</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -14672,17 +14672,17 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>2.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -14711,17 +14711,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CAPLIPOINT</t>
+          <t>ELECON</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Caplin Point Laboratories Ltd.</t>
+          <t>Elecon Engineering Co. Ltd.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -14730,31 +14730,31 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2560.8</v>
+        <v>451.55</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>1703.23 - 1716.1 DR DEMAND</t>
+          <t>450.65 - 452.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>630.8 - 668.52 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
           <t>4.0 C</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>2503.19 - 2628.59 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>7.0 A</t>
-        </is>
-      </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>8.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -14789,12 +14789,12 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
@@ -14813,17 +14813,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>APARINDS</t>
+          <t>CAPLIPOINT</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Apar Industries Ltd.</t>
+          <t>Caplin Point Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -14832,26 +14832,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>16858</v>
+        <v>2560.8</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>13401.0 - 13443.0 DR DEMAND</t>
+          <t>1703.23 - 1716.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>15849.0 - 17157.0 RD SUPPLY</t>
+          <t>2503.19 - 2628.59 RD SUPPLY</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -14915,17 +14915,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>APARINDS</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Bajaj Finserv Ltd.</t>
+          <t>Apar Industries Ltd.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -14934,21 +14934,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2024.5</v>
+        <v>16856</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2108.2 - 2116.19 RD SUPPLY</t>
+          <t>13401.0 - 13443.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>1991.7 - 2073.13 RD SUPPLY</t>
+          <t>15849.0 - 17157.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -15017,17 +15017,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Hero MotoCorp Ltd.</t>
+          <t>Bajaj Finserv Ltd.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -15036,21 +15036,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5735</v>
+        <v>2032.5</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>4982.0 - 5011.1 DR DEMAND</t>
+          <t>2108.2 - 2116.19 RD SUPPLY</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>5627.23 - 5755.34 RD SUPPLY</t>
+          <t>1991.7 - 2073.13 RD SUPPLY</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -15065,7 +15065,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -15119,17 +15119,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>JUBLINGREA</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Jubilant Ingrevia Ltd.</t>
+          <t>Hero MotoCorp Ltd.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -15138,21 +15138,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>718.35</v>
+        <v>5735</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>538.29 - 548.2 DR DEMAND</t>
+          <t>4982.0 - 5011.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>711.35 - 766.92 RD SUPPLY</t>
+          <t>5627.23 - 5755.34 RD SUPPLY</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -15221,17 +15221,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>JUBLINGREA</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Max Financial Services Ltd.</t>
+          <t>Jubilant Ingrevia Ltd.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -15240,36 +15240,36 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1585</v>
+        <v>718.35</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>1584.5 - 1587.9 RD SUPPLY</t>
+          <t>538.29 - 548.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>1467.5 - 1499.0 DR DEMAND</t>
+          <t>711.35 - 766.92 RD SUPPLY</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -15299,12 +15299,12 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
@@ -15323,17 +15323,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>National Aluminium Co. Ltd.</t>
+          <t>Max Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -15342,36 +15342,36 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>394.45</v>
+        <v>1585</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>392.0 - 395.75 RD SUPPLY</t>
+          <t>1584.5 - 1587.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>131.8 - 149.71 DR DEMAND</t>
+          <t>1467.5 - 1499.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -15425,17 +15425,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PTCIL</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PTC Industries Ltd.</t>
+          <t>National Aluminium Co. Ltd.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -15444,11 +15444,11 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>20629</v>
+        <v>394.45</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>20584.0 - 20750.0 RD SUPPLY</t>
+          <t>392.0 - 395.75 RD SUPPLY</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>11902.0 - 12721.0 DR DEMAND</t>
+          <t>131.8 - 149.71 DR DEMAND</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -15527,17 +15527,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>PTCIL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Container Corporation of India Ltd.</t>
+          <t>PTC Industries Ltd.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -15546,26 +15546,26 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>515.05</v>
+        <v>20629</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>498.25 - 501.9 DR DEMAND</t>
+          <t>20584.0 - 20750.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>507.3 - 535.36 RD SUPPLY</t>
+          <t>11902.0 - 12721.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -15575,7 +15575,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -15590,7 +15590,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -15605,12 +15605,12 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
@@ -15629,17 +15629,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Amber Enterprises India Ltd.</t>
+          <t>Container Corporation of India Ltd.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -15648,31 +15648,31 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>7350</v>
+        <v>515.05</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>7350.0 - 7408.0 RD SUPPLY</t>
+          <t>498.25 - 501.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>6120.0 - 6549.0 DR DEMAND</t>
+          <t>507.3 - 535.36 RD SUPPLY</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -15692,7 +15692,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -15707,12 +15707,12 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
@@ -15731,12 +15731,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Bata India Ltd.</t>
+          <t>Amber Enterprises India Ltd.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -15750,31 +15750,31 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>701.05</v>
+        <v>7350</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>625.59 - 627.84 DR DEMAND</t>
+          <t>7350.0 - 7408.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>685.67 - 743.46 RD SUPPLY</t>
+          <t>6120.0 - 6549.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -15809,12 +15809,12 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
@@ -15833,12 +15833,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Kajaria Ceramics Ltd.</t>
+          <t>Bata India Ltd.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -15852,21 +15852,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1208.5</v>
+        <v>701.05</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>1060.5 - 1072.6 DR DEMAND</t>
+          <t>625.59 - 627.84 DR DEMAND</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>1187.65 - 1246.8 RD SUPPLY</t>
+          <t>685.67 - 743.46 RD SUPPLY</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -15935,17 +15935,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Kfin Technologies Ltd.</t>
+          <t>Kajaria Ceramics Ltd.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -15954,28 +15954,28 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>980</v>
+        <v>1208.5</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>974.0 - 982.5 RD SUPPLY</t>
+          <t>1060.5 - 1072.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
+          <t>2.5 C</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>1187.65 - 1246.8 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
           <t>5.0 C</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>1329.97 - 1360.84 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>6.5 B</t>
-        </is>
-      </c>
       <c r="J152" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -15988,7 +15988,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -16013,12 +16013,12 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
@@ -16037,17 +16037,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PCBL Chemical Ltd.</t>
+          <t>Kfin Technologies Ltd.</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -16056,26 +16056,26 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>317.55</v>
+        <v>980</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>308.15 - 309.8 DR DEMAND</t>
+          <t>974.0 - 982.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>305.14 - 326.1 RD SUPPLY</t>
+          <t>1329.97 - 1360.84 RD SUPPLY</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -16090,7 +16090,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -16115,12 +16115,12 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
@@ -16139,17 +16139,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>RAILTEL</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Railtel Corporation Of India Ltd.</t>
+          <t>PCBL Chemical Ltd.</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -16158,31 +16158,31 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>287.25</v>
+        <v>317.55</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>287.25 - 297.6 RD SUPPLY</t>
+          <t>308.15 - 309.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>425.02 - 472.75 RD SUPPLY</t>
+          <t>305.14 - 326.1 RD SUPPLY</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -16192,7 +16192,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -16217,12 +16217,12 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
@@ -16241,17 +16241,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>RAILTEL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Engineers India Ltd.</t>
+          <t>Railtel Corporation Of India Ltd.</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -16260,31 +16260,31 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>244.91</v>
+        <v>287.25</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>244.78 - 249.0 RD SUPPLY</t>
+          <t>287.25 - 297.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>219.44 - 222.38 DR DEMAND</t>
+          <t>425.02 - 472.75 RD SUPPLY</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -16294,7 +16294,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -16343,17 +16343,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PVR INOX Ltd.</t>
+          <t>Engineers India Ltd.</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -16362,26 +16362,26 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1216.8</v>
+        <v>244.91</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>1130.0 - 1135.0 DR DEMAND</t>
+          <t>244.78 - 249.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>1207.7 - 1249.7 RD SUPPLY</t>
+          <t>219.44 - 222.38 DR DEMAND</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -16421,12 +16421,12 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
@@ -16445,17 +16445,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Home First Finance Company India Ltd.</t>
+          <t>PVR INOX Ltd.</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -16464,26 +16464,26 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1193.7</v>
+        <v>1216.8</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>1135.3 - 1139.4 DR DEMAND</t>
+          <t>1130.0 - 1135.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>1184.37 - 1233.14 RD SUPPLY</t>
+          <t>1207.7 - 1249.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -16508,7 +16508,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -16547,17 +16547,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>AU Small Finance Bank Ltd.</t>
+          <t>Home First Finance Company India Ltd.</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -16566,26 +16566,26 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1105</v>
+        <v>1193.7</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>1087.6 - 1105.9 RD SUPPLY</t>
+          <t>1135.3 - 1139.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>830.84 - 841.88 DR DEMAND</t>
+          <t>1184.37 - 1233.14 RD SUPPLY</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -16595,7 +16595,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -16610,7 +16610,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>3.5 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -16625,12 +16625,12 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="S158" t="inlineStr">
@@ -16770,7 +16770,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>155.25</v>
+        <v>155.24</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -21518,7 +21518,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>550.35 - 680.07 DR DEMAND</t>
+          <t>550.35 - 680.06 DR DEMAND</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -23472,7 +23472,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>151235.03 - 159415.43 RD SUPPLY</t>
+          <t>151235.04 - 159415.43 RD SUPPLY</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -30724,7 +30724,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>4335.0 - 4897.45 RD SUPPLY</t>
+          <t>4334.99 - 4897.45 RD SUPPLY</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -33580,7 +33580,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>10163.48 - 12763.22 DR DEMAND</t>
+          <t>10163.49 - 12763.22 DR DEMAND</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -34192,7 +34192,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>1598.44 - 1928.41 RD SUPPLY</t>
+          <t>1598.43 - 1928.41 RD SUPPLY</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -33272,7 +33272,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>151235.04 - 159415.43 RD SUPPLY</t>
+          <t>151235.03 - 159415.43 RD SUPPLY</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -33374,7 +33374,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>10163.48 - 12763.22 DR DEMAND</t>
+          <t>10163.49 - 12763.22 DR DEMAND</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -36522,11 +36522,11 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>2515</v>
+        <v>2512.5</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>2252.1 - 2342.0 DR DEMAND</t>
+          <t>2249.86 - 2339.67 DR DEMAND</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -36536,7 +36536,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>1274.17 - 1542.62 DR DEMAND</t>
+          <t>1272.91 - 1541.08 DR DEMAND</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -30094,7 +30094,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>4335.0 - 4897.45 RD SUPPLY</t>
+          <t>4334.99 - 4897.45 RD SUPPLY</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -37444,7 +37444,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>6402.71 - 6552.65 RD SUPPLY</t>
+          <t>6402.72 - 6552.65 RD SUPPLY</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -13894,7 +13894,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>10163.49 - 12763.22 DR DEMAND</t>
+          <t>10163.48 - 12763.22 DR DEMAND</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -35292,7 +35292,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>1598.44 - 1928.41 RD SUPPLY</t>
+          <t>1598.43 - 1928.41 RD SUPPLY</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -13588,7 +13588,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>10163.49 - 12763.22 DR DEMAND</t>
+          <t>10163.48 - 12763.22 DR DEMAND</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -34036,7 +34036,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>1598.43 - 1928.41 RD SUPPLY</t>
+          <t>1598.44 - 1928.41 RD SUPPLY</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -38218,7 +38218,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>550.35 - 680.06 DR DEMAND</t>
+          <t>550.35 - 680.07 DR DEMAND</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -13926,7 +13926,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>10163.49 - 12763.22 DR DEMAND</t>
+          <t>10163.48 - 12763.22 DR DEMAND</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -31408,7 +31408,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>4334.99 - 4897.45 RD SUPPLY</t>
+          <t>4335.0 - 4897.45 RD SUPPLY</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -36406,7 +36406,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>1598.43 - 1928.41 RD SUPPLY</t>
+          <t>1598.44 - 1928.41 RD SUPPLY</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -40384,7 +40384,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>550.35 - 680.07 DR DEMAND</t>
+          <t>550.35 - 680.06 DR DEMAND</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -32726,7 +32726,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>4334.99 - 4897.45 RD SUPPLY</t>
+          <t>4335.0 - 4897.45 RD SUPPLY</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -918,7 +918,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10163.48 - 12763.22 DR DEMAND</t>
+          <t>10163.49 - 12763.22 DR DEMAND</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>101787.0 - 115617.15 DR DEMAND</t>
+          <t>101786.99 - 115617.15 DR DEMAND</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -31172,7 +31172,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>1598.43 - 1928.41 RD SUPPLY</t>
+          <t>1598.44 - 1928.41 RD SUPPLY</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -39230,7 +39230,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>550.35 - 680.07 DR DEMAND</t>
+          <t>550.35 - 680.06 DR DEMAND</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -698,7 +698,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10163.49 - 12763.22 DR DEMAND</t>
+          <t>10163.48 - 12763.22 DR DEMAND</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -30858,7 +30858,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>4335.0 - 4897.45 RD SUPPLY</t>
+          <t>4334.99 - 4897.45 RD SUPPLY</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -31940,7 +31940,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>4334.99 - 4897.45 RD SUPPLY</t>
+          <t>4335.0 - 4897.45 RD SUPPLY</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -32348,7 +32348,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>1598.43 - 1928.41 RD SUPPLY</t>
+          <t>1598.44 - 1928.41 RD SUPPLY</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -39394,7 +39394,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>550.35 - 680.06 DR DEMAND</t>
+          <t>550.35 - 680.07 DR DEMAND</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -9050,7 +9050,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>10163.48 - 12763.22 DR DEMAND</t>
+          <t>10163.49 - 12763.22 DR DEMAND</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -37910,7 +37910,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>550.35 - 680.06 DR DEMAND</t>
+          <t>550.35 - 680.07 DR DEMAND</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
